--- a/astro-site/public/dl/plan-negocio-bar-restaurante/plan-financiero-bar-restaurante.xlsx
+++ b/astro-site/public/dl/plan-negocio-bar-restaurante/plan-financiero-bar-restaurante.xlsx
@@ -1685,7 +1685,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
         <v>0.020389375627043124</v>
       </c>
       <c r="D13" s="44" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Obra civil y reforma local, Proyecto técnico + licencia actividad y Decoración e interiorismo), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Obra civil y reforma local, Proyecto técnico + licencia actividad y Decoración e interiorismo), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no "&amp;"financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Obra civil y reforma local, Proyecto técnico + licencia actividad y Decoración e interiorismo), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E13" s="44" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C50" s="44" t="n"/>
       <c r="D50" s="44" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E50" s="44" t="n"/>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C55" s="44" t="n"/>
       <c r="D55" s="41" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Honorarios inmobiliaria, Fianza del alquiler, Alquiler de los meses previos a la apertura, Diseño marca e identidad visual, Web + Google My Business, Campaña lanzamiento RRSS + inauguración, Constitución SL (notaría + registro), Licencias y permisos varios, Primera compra de despensa y cámaras, Primera compra de bodega y barra ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B48-B53-B54,"0")&amp;" € de los "&amp;TEXT(B48,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Honorarios inmobiliaria, Fianza del alquiler, Alquiler de los meses previos a la apertura, Diseño marca e identidad visual, Web + Google My Business, Campaña lanzamiento RRSS + inauguración, "&amp;"Constitución SL (notaría + registro), Licencias y permisos varios, Primera compra de despensa y cámaras, Primera compra de bodega y barra ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B48-B53-B54,"0")&amp;" € de los "&amp;TEXT(B48,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Honorarios inmobiliaria, Fianza del alquiler, Alquiler de los meses previos a la apertura, Diseño marca e identidad visual, Web + Google My Business, Campaña lanzamiento RRSS + inauguración, Constitución SL (notaría + registro), Licencias y permisos varios, Primera compra de despensa y cámaras, Primera compra de bodega y barra ni Colchón operativo hasta alcanzar el equilibrio. Suman 91405 € de los 179015 € de inversión.</v>
       </c>
       <c r="E55" s="44" t="n"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="E25" s="44" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F25" s="44" t="n"/>

--- a/astro-site/public/dl/plan-negocio-bar-restaurante/plan-financiero-bar-restaurante.xlsx
+++ b/astro-site/public/dl/plan-negocio-bar-restaurante/plan-financiero-bar-restaurante.xlsx
@@ -1685,7 +1685,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-bar-restaurante/plan-financiero-bar-restaurante.xlsx
+++ b/astro-site/public/dl/plan-negocio-bar-restaurante/plan-financiero-bar-restaurante.xlsx
@@ -1685,7 +1685,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
         <v>0.020389375627043124</v>
       </c>
       <c r="D13" s="44" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Obra civil y reforma local, Proyecto técnico + licencia actividad y Decoración e interiorismo), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Obra civil y reforma local, Proyecto técnico + licencia actividad y Decoración e interiorismo), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no "&amp;"financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Obra civil y reforma local, Proyecto técnico + licencia actividad y Decoración e interiorismo), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E13" s="44" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C50" s="44" t="n"/>
       <c r="D50" s="44" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E50" s="44" t="n"/>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C55" s="44" t="n"/>
       <c r="D55" s="41" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Honorarios inmobiliaria, Fianza del alquiler, Alquiler de los meses previos a la apertura, Diseño marca e identidad visual, Web + Google My Business, Campaña lanzamiento RRSS + inauguración, Constitución SL (notaría + registro), Licencias y permisos varios, Primera compra de despensa y cámaras, Primera compra de bodega y barra ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B48-B53-B54,"0")&amp;" € de los "&amp;TEXT(B48,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Honorarios inmobiliaria, Fianza del alquiler, Alquiler de los meses previos a la apertura, Diseño marca e identidad visual, Web + Google My Business, Campaña lanzamiento RRSS + inauguración, "&amp;"Constitución SL (notaría + registro), Licencias y permisos varios, Primera compra de despensa y cámaras, Primera compra de bodega y barra ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B48-B53-B54,"0")&amp;" € de los "&amp;TEXT(B48,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Honorarios inmobiliaria, Fianza del alquiler, Alquiler de los meses previos a la apertura, Diseño marca e identidad visual, Web + Google My Business, Campaña lanzamiento RRSS + inauguración, Constitución SL (notaría + registro), Licencias y permisos varios, Primera compra de despensa y cámaras, Primera compra de bodega y barra ni Colchón operativo hasta alcanzar el equilibrio. Suman 91405 € de los 179015 € de inversión.</v>
       </c>
       <c r="E55" s="44" t="n"/>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="E25" s="44" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F25" s="44" t="n"/>
